--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>4.047</t>
-  </si>
-  <si>
-    <t>(2.341)</t>
-  </si>
-  <si>
-    <t>7.319</t>
-  </si>
-  <si>
-    <t>(0.852)</t>
-  </si>
-  <si>
-    <t>71.605</t>
-  </si>
-  <si>
-    <t>(21.546)</t>
-  </si>
-  <si>
-    <t>87.096</t>
-  </si>
-  <si>
-    <t>(28.221)</t>
-  </si>
-  <si>
-    <t>1.162</t>
-  </si>
-  <si>
-    <t>(0.169)</t>
-  </si>
-  <si>
-    <t>7.187</t>
-  </si>
-  <si>
-    <t>(0.823)</t>
-  </si>
-  <si>
-    <t>6.606</t>
-  </si>
-  <si>
-    <t>(2.609)</t>
-  </si>
-  <si>
-    <t>3.676</t>
-  </si>
-  <si>
-    <t>(2.390)</t>
-  </si>
-  <si>
-    <t>100.205</t>
-  </si>
-  <si>
-    <t>(35.311)</t>
-  </si>
-  <si>
-    <t>75.909</t>
-  </si>
-  <si>
-    <t>(21.693)</t>
+    <t>1.774</t>
+  </si>
+  <si>
+    <t>(0.331)</t>
+  </si>
+  <si>
+    <t>7.621</t>
+  </si>
+  <si>
+    <t>(0.878)</t>
+  </si>
+  <si>
+    <t>49.042</t>
+  </si>
+  <si>
+    <t>(10.819)</t>
+  </si>
+  <si>
+    <t>56.770</t>
+  </si>
+  <si>
+    <t>(12.156)</t>
+  </si>
+  <si>
+    <t>1.216</t>
+  </si>
+  <si>
+    <t>(0.175)</t>
+  </si>
+  <si>
+    <t>7.517</t>
+  </si>
+  <si>
+    <t>(0.845)</t>
+  </si>
+  <si>
+    <t>3.808</t>
+  </si>
+  <si>
+    <t>(1.166)</t>
+  </si>
+  <si>
+    <t>0.930</t>
+  </si>
+  <si>
+    <t>(0.423)</t>
+  </si>
+  <si>
+    <t>63.964</t>
+  </si>
+  <si>
+    <t>(12.404)</t>
+  </si>
+  <si>
+    <t>51.618</t>
+  </si>
+  <si>
+    <t>(12.447)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(26.863)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-1.765</t>
-  </si>
-  <si>
-    <t>0.725</t>
-  </si>
-  <si>
-    <t>41.872</t>
-  </si>
-  <si>
-    <t>34.195</t>
-  </si>
-  <si>
-    <t>0.763*</t>
-  </si>
-  <si>
-    <t>0.813</t>
-  </si>
-  <si>
-    <t>-3.356</t>
-  </si>
-  <si>
-    <t>-3.319</t>
-  </si>
-  <si>
-    <t>41.852</t>
-  </si>
-  <si>
-    <t>26.759</t>
+    <t>0.507</t>
+  </si>
+  <si>
+    <t>0.423</t>
+  </si>
+  <si>
+    <t>64.435**</t>
+  </si>
+  <si>
+    <t>64.521**</t>
+  </si>
+  <si>
+    <t>0.710</t>
+  </si>
+  <si>
+    <t>0.483</t>
+  </si>
+  <si>
+    <t>-0.557</t>
+  </si>
+  <si>
+    <t>-0.573</t>
+  </si>
+  <si>
+    <t>78.092***</t>
+  </si>
+  <si>
+    <t>51.049*</t>
   </si>
 </sst>
 </file>
